--- a/docs/build/lakeshore-enterprise-context/source/07_data_analytics_reporting/data_quality_issues.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/07_data_analytics_reporting/data_quality_issues.xlsx
@@ -485,22 +485,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Bank account</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Inconsistent mapping</t>
+          <t>Duplicates</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Remediating</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bank account</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -539,17 +539,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bank account</t>
+          <t>Vendor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Missing values</t>
+          <t>Duplicates</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -566,17 +566,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bank account</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Duplicates</t>
+          <t>Inconsistent mapping</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -603,12 +603,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Remediating</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -620,22 +620,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Inconsistent mapping</t>
+          <t>Duplicates</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Remediating</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Missing values</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -674,17 +674,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Bank account</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Inconsistent mapping</t>
+          <t>Duplicates</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,12 +701,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Bank account</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Missing values</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Remediating</t>
         </is>
       </c>
     </row>
@@ -728,12 +728,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Duplicates</t>
+          <t>Missing values</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Remediating</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -760,17 +760,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Inconsistent mapping</t>
+          <t>Missing values</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Remediating</t>
         </is>
       </c>
     </row>
@@ -782,12 +782,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bank account</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Duplicates</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Bank account</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -819,12 +819,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -841,17 +841,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Missing values</t>
+          <t>Inconsistent mapping</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -863,22 +863,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bank account</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Duplicates</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -890,12 +890,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Duplicates</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -917,22 +917,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Bank account</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Duplicates</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Remediating</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -944,17 +944,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bank account</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Missing values</t>
+          <t>Inconsistent mapping</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Vendor</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Missing values</t>
+          <t>Inconsistent mapping</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1025,22 +1025,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bank account</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Inconsistent mapping</t>
+          <t>Missing values</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Bank account</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Bank account</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Remediating</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Bank account</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bank account</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Remediating</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Bank account</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Duplicates</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Remediating</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Vendor</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Vendor</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1251,12 +1251,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Remediating</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1268,22 +1268,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bank account</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Duplicates</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Remediating</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Inconsistent mapping</t>
+          <t>Duplicates</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Remediating</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Vendor</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Duplicates</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Vendor</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Missing values</t>
+          <t>Inconsistent mapping</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Bank account</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Missing values</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Duplicates</t>
+          <t>Inconsistent mapping</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,22 +1457,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Bank account</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Inconsistent mapping</t>
+          <t>Missing values</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Vendor</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1521,12 +1521,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Remediating</t>
         </is>
       </c>
     </row>
@@ -1538,12 +1538,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Bank account</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Duplicates</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Remediating</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
